--- a/DateBase/orders/Nha Thu_2026-6-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-13.xlsx
@@ -606,6 +606,9 @@
       <c r="C21" t="str">
         <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -664,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151510101516161515127855101010550</v>
+        <v>0151510101516161515127855101010555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,9 +610,128 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>356_绿枫叶山货_maple leaf small_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>5</v>
+      </c>
+      <c r="C23" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>344_钢草_steal grass_Xanthorrhoea preissii Endl._1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>457_茴香花_lace flower yellow_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +786,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0151510101516161515127855101010555</v>
+        <v>01515101015161615151278551010105551010510101010105520101030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-6-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-13.xlsx
@@ -788,6 +788,9 @@
       <c r="G2" t="str">
         <v>01515101015161615151278551010105551010510101010105520101030</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
